--- a/research/KMD.NZ/Reports/KMD.NZ_DCF_Model.xlsx
+++ b/research/KMD.NZ/Reports/KMD.NZ_DCF_Model.xlsx
@@ -2376,9 +2376,10 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="9">
-        <f> Owner FCF</f>
-        <v>0</v>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>= Owner FCF</t>
+        </is>
       </c>
       <c r="B8" s="14">
         <v>72.8</v>
